--- a/entertainment_forms/044_villain_character_profile--entertainment_forms.xlsx
+++ b/entertainment_forms/044_villain_character_profile--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4.1,_'label':_'actor',_'description':_'actor'}</t>
+          <t>actor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4.1, 'label': 'actor', 'description': 'Actor'}</t>
+          <t>actor</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4.2,_'label':_'actress',_'description':_'actress'}</t>
+          <t>actress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4.2, 'label': 'actress', 'description': 'Actress'}</t>
+          <t>actress</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4.3,_'label':_'musician',_'description':_'musician'}</t>
+          <t>musician</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4.3, 'label': 'musician', 'description': 'Musician'}</t>
+          <t>musician</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'telepathy',_'description':_'telepathy'}</t>
+          <t>telepathy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'telepathy', 'description': 'Telepathy'}</t>
+          <t>telepathy</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'telekinesis',_'description':_'telekinesis'}</t>
+          <t>telekinesis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'telekinesis', 'description': 'Telekinesis'}</t>
+          <t>telekinesis</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'mind_control',_'description':_'mind_control'}</t>
+          <t>mind_control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': 'mind_control', 'description': 'Mind control'}</t>
+          <t>mind control</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'label':_'weakness1',_'description':_'weakness_1'}</t>
+          <t>weakness1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'label': 'weakness1', 'description': 'Weakness 1'}</t>
+          <t>weakness1</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'label':_'weakness2',_'description':_'weakness_2'}</t>
+          <t>weakness2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'label': 'weakness2', 'description': 'Weakness 2'}</t>
+          <t>weakness2</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'label':_'weakness3',_'description':_'weakness_3'}</t>
+          <t>weakness3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'label': 'weakness3', 'description': 'Weakness 3'}</t>
+          <t>weakness3</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'label':_'power',_'description':_'power'}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'label': 'power', 'description': 'Power'}</t>
+          <t>power</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'label':_'revenge',_'description':_'revenge'}</t>
+          <t>revenge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'label': 'revenge', 'description': 'Revenge'}</t>
+          <t>revenge</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'label':_'chaos',_'description':_'chaos'}</t>
+          <t>chaos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'label': 'chaos', 'description': 'Chaos'}</t>
+          <t>chaos</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_'underground',_'description':_'underground'}</t>
+          <t>underground</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 'underground', 'description': 'Underground'}</t>
+          <t>underground</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'label':_'fortress',_'description':_'fortress'}</t>
+          <t>fortress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'label': 'fortress', 'description': 'Fortress'}</t>
+          <t>fortress</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12.1,_'label':_'world_domination',_'description':_'world_domination'}</t>
+          <t>world_domination</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12.1, 'label': 'world Domination', 'description': 'World Domination'}</t>
+          <t>world Domination</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_12.2,_'label':_'wealth',_'description':_'wealth'}</t>
+          <t>wealth</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 12.2, 'label': 'wealth', 'description': 'Wealth'}</t>
+          <t>wealth</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_12.3,_'label':_'destruction',_'description':_'destruction'}</t>
+          <t>destruction</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 12.3, 'label': 'destruction', 'description': 'Destruction'}</t>
+          <t>destruction</t>
         </is>
       </c>
     </row>
